--- a/docs/CodeSystem-BRMotivoRealizacaoExame.xlsx
+++ b/docs/CodeSystem-BRMotivoRealizacaoExame.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:42:43-04:00</t>
+    <t>2026-09-10T12:01:58-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
